--- a/documentation/Construccion y Evolucion/2. Reportes de problemas/PR 3.xlsx
+++ b/documentation/Construccion y Evolucion/2. Reportes de problemas/PR 3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\TraductorBraille\documentation\Construccion y Evolucion\2. Reportes de problemas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D7DAACA-E0D1-4640-8546-1A1F0AC10961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E28523-859B-40C7-BF71-BDB8B43CA4FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{AAACD53E-982C-4521-B07F-7DC6290E23F5}"/>
+    <workbookView xWindow="-11616" yWindow="-1980" windowWidth="11712" windowHeight="12336" xr2:uid="{AAACD53E-982C-4521-B07F-7DC6290E23F5}"/>
   </bookViews>
   <sheets>
     <sheet name="PR Formato" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="16">
   <si>
     <t>Reporte de Problema</t>
   </si>
@@ -65,6 +65,17 @@
   </si>
   <si>
     <t>No hay un estándar en la forma de escribir código. Se mezclan idiomas (inglés y español) y las variables no están nombradas de manera consistente.</t>
+  </si>
+  <si>
+    <t>La falta de un estándar puede resultar de la ausencia de normas de codificación, la colaboración de múltiples desarrolladores con estilos variados, y una comunicación inadecuada sobre las mejores prácticas.</t>
+  </si>
+  <si>
+    <t>Establecer un conjunto de normas que especifiquen el idioma y el formato para nombres de variables, comentarios y documentación. 
+Asegurar que todos los miembros del equipo sigan las mismas normas de codificación. 
+Introducir un proceso de revisión de código que verifique el cumplimiento de las normas establecidas y garantice la consistencia en el proyecto.</t>
+  </si>
+  <si>
+    <t> La aplicación de estándares de codificación consistentes mejorará la legibilidad y mantenibilidad del código, facilitando la colaboración y reduciendo los errores. Es recomendable revisar periódicamente estos estándares para adaptarse a las nuevas prácticas y necesidades del proyecto.</t>
   </si>
 </sst>
 </file>
@@ -355,32 +366,32 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -717,7 +728,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F84A08-0160-4953-9528-DB07A5F993CD}">
   <dimension ref="B1:H28"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="5.5703125" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -969,26 +980,26 @@
       <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="23"/>
+      <c r="C18" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="26"/>
       <c r="H18" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="24"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="26"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="29"/>
       <c r="H19" s="9" t="s">
         <v>8</v>
       </c>
@@ -1025,26 +1036,26 @@
       <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="23"/>
+      <c r="C22" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="26"/>
       <c r="H22" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="24"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="26"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="29"/>
       <c r="H23" s="9" t="s">
         <v>8</v>
       </c>
@@ -1085,17 +1096,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="29"/>
+      <c r="C26" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="23"/>
       <c r="H26" s="9" t="s">
         <v>8</v>
       </c>
